--- a/assets/infobasica/planilhas/aula29_nivel1.xlsx
+++ b/assets/infobasica/planilhas/aula29_nivel1.xlsx
@@ -451,7 +451,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <f>_xlfn._xlws.FILTER(A2:A20,MOD(A2:A20,2)=0)</f>
+        <f>FILTER(A2:A20,MOD(A2:A20,2)=0)</f>
         <v/>
       </c>
     </row>
@@ -577,9 +577,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <f>FILTRO(A2:A20; MOD(A2:A20; 2)=0) mostra só os números pares.</f>
-        <v/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>=FILTRO(A2:A20; MOD(A2:A20; 2)=0) mostra só os números pares.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -592,7 +593,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
